--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>1.881544797159837</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.7822599407481463</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,7 +999,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,19 +1096,19 @@
         <v>1.459631575266611</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>1.582654486293763</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>-0.02757616914688643</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1393,19 +1394,19 @@
         <v>2.313057072685344</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>2.010342128958591</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.2173137192430232</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,15 +1585,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
@@ -1600,15 +1601,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>2.234628720650876</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,19 +1720,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>1.954572436250566</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>0.03244559623895604</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,15 +1883,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
@@ -1898,15 +1899,15 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1959791867971223</v>
+        <v>0.09697834317649545</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.3192374434349921</v>
+        <v>0.03837250935283798</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1493682538447889</v>
+        <v>0.07784184823645553</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1913411920973691</v>
+        <v>0.2927487227303591</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3962590803105496</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.140120856124863</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8422821421943985</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.9809477008984322</v>
+        <v>0.3127612378554672</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1571031582729965</v>
+        <v>0.03171779927911134</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.377757118100216</v>
+        <v>1.14815466838371</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1449635134974329</v>
+        <v>-0.06187989028444074</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1064175444416622</v>
+        <v>-0.02253080101627258</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2370962427828502</v>
+        <v>0.002909733197253406</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1056334130053012</v>
+        <v>-0.02536672381513549</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1352489334146483</v>
+        <v>-0.1119345220901933</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2522482975569502</v>
+        <v>-0.1593792306814323</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1305473168703624</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.06914337196566545</v>
+        <v>0.1014896750783869</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1026878098195446</v>
+        <v>0.2631420798182799</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.07296209010827437</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.750643729813145</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.1550870847103764</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1305473168703624</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2245981758688171</v>
+        <v>0.06275383040083748</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2846926669136679</v>
+        <v>-0.164766591625006</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3154518179023966</v>
+        <v>0.2303709495067841</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07493175475241953</v>
+        <v>-0.05186177108960599</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.05077868749966463</v>
+        <v>-0.1904439286027694</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.5354896109552609</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3818119603493736</v>
+        <v>-0.1904439286027694</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1417989242640241</v>
+        <v>0.08803243247990244</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2594733339773532</v>
+        <v>0.02990453202561993</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3762018586691143</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1489282515644331</v>
+        <v>0.07678140322463056</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1648590707975937</v>
+        <v>0.293042431667241</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9761772853185595</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3347200994649614</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2563327497344814</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7114758409874703</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3762018586691143</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7162684808991735</v>
+        <v>0.3020556073634397</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.002499802893409786</v>
+        <v>0.02330409142986589</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.006010817014844</v>
+        <v>1.108854019391227</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05803538094404992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.0453020112149235</v>
+        <v>-0.008155047683702232</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1019294515886753</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1336124219126114</v>
+        <v>-0.008155047683702343</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1371268527137726</v>
+        <v>0.01470711644675537</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1092613383823048</v>
+        <v>-0.002901291213893376</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.03128360262353591</v>
+        <v>0.01765964342896953</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1586910844842336</v>
+        <v>-0.1119345220901933</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.07198533628632553</v>
+        <v>-0.1593792306814323</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.546578367816291</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3321549373629414</v>
+        <v>0.1014896750783869</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.17240925781718</v>
+        <v>0.2631420798182799</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4952242688027606</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.0467677110577891</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.052641008672777</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5217129259898844</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.6666984237144864</v>
+        <v>0.06275383040083748</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.02645485840237338</v>
+        <v>-0.164766591625006</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9363888595258903</v>
+        <v>0.2303709495067841</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1232553819783047</v>
+        <v>-0.05186177108960599</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2965522102697927</v>
+        <v>-0.1904439286027694</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.1639199617993696</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1586358272060501</v>
+        <v>-0.1904439286027694</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.04057849384149836</v>
+        <v>0.08803243247990244</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1478210716904058</v>
+        <v>0.02990453202561993</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4525292958562871</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2197664227545297</v>
+        <v>0.07678140322463056</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1821151144805237</v>
+        <v>0.293042431667241</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.992797783933518</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4471675687328562</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.04398387499408551</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9504924339323556</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4525292958562871</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.8822674557214283</v>
+        <v>0.3020556073634397</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.09946245261394315</v>
+        <v>0.02330409142986589</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.239159096937649</v>
+        <v>1.108854019391227</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1235425903287488</v>
+        <v>-0.05803538094404992</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1299359509522845</v>
+        <v>-0.008155047683702232</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.08432174590467179</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04981466453266226</v>
+        <v>-0.008155047683702343</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2136205238079618</v>
+        <v>0.01470711644675537</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.2598164779520239</v>
+        <v>-0.002901291213893376</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.06241148683808073</v>
+        <v>0.01765964342896953</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.06243098569167893</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1719256930745958</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3230679747701246</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1976390706274396</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1231478139061114</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9795013850415513</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2886086895356375</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.3434107967099744</v>
+        <v>0.2117597153840087</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.6134621447349152</v>
+        <v>-0.03587709265072071</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3230679747701246</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4934551070045745</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1276490438035387</v>
+        <v>-0.2060850325577076</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6930657827280531</v>
+        <v>0.03737143334716841</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08899901788117059</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1116643187270596</v>
+        <v>-0.07351729141350127</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1783056063688457</v>
+        <v>0.2039938033319573</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2460905927363766</v>
+        <v>-0.2304921287613514</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05125509861622679</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.04687658655894855</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1107025905166326</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.2251721953906756</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.440783672775422</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1874961465207722</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.169748614901844</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9822714681440443</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3934249858247302</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1454728376224452</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8362580350046616</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.440783672775422</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.831105081086797</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.069577693290096</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.167300703501166</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.07130274274158876</v>
+        <v>-0.02253080101627258</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.004694222957882577</v>
+        <v>0.002909733197253406</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.07564188582246567</v>
+        <v>-0.02536672381513549</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1606267797144658</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.1878609050676436</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.03353381892721941</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.05125509861622679</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.01065023267654031</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.09147296701545193</v>
+        <v>0.1992071128489044</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0361281855360438</v>
+        <v>0.3195988776620315</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2171366704425773</v>
+        <v>0.1494510221753559</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2748323219326458</v>
+        <v>0.1914457407943713</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9811046511627907</v>
+        <v>0.9706045479755963</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5315036835710507</v>
+        <v>-0.3956369736729515</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.05638459704404664</v>
+        <v>0.1419415286399084</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.055598642040589</v>
+        <v>0.8404247724914087</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.329736496831094</v>
+        <v>0.9842496324385637</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.09804077200338912</v>
+        <v>0.1555748210976431</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.18544284932526</v>
+        <v>1.372521618076181</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.197128506330739</v>
+        <v>-0.1449635134974329</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.3294578948487177</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.4629259009092757</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1029808820995737</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1532558675077065</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.2514292974161799</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.414421357968767</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.5340941927569753</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>0.7759950933958086</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.03429285245675695</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.082113730200731</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1729929842825908</v>
+        <v>0.1086140839261553</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.186809944462409</v>
+        <v>0.2386110168472386</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0116421001056547</v>
+        <v>-0.1049537999847421</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.03081137871963469</v>
+        <v>0.1362058923346454</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.07995554818428363</v>
+        <v>0.2502727879555997</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2466901429950641</v>
+        <v>-0.1305473168703624</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0967716574308219</v>
+        <v>0.06917602495951546</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09708356730186078</v>
+        <v>0.1027439460874294</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3582848837209303</v>
+        <v>0.9722684414864116</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.07200685182933619</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.7534393535449486</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.1529592684543117</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1305473168703624</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>-0.05186929266720175</v>
+        <v>0.2243688378243176</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.553131362600058</v>
+        <v>-0.2869597768363595</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-0.0462408020223753</v>
+        <v>0.3128790402222748</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.246690142995064</v>
+        <v>-0.07493175475241953</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1120360736642554</v>
+        <v>-0.0525357295159713</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.181895334740688</v>
+        <v>0.5354896109552609</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5930309249039774</v>
+        <v>-0.3829562481412093</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1280357344784944</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.09250707423188109</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3669,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1255881729100359</v>
+        <v>0.1457505928835738</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.06851352850921844</v>
+        <v>0.260775707757388</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3762018586691142</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1718439122094128</v>
+        <v>0.1490107702765023</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2198628215274138</v>
+        <v>0.1649473667952948</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9752906976744186</v>
+        <v>0.9761508596783139</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.3340345818389634</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.2583390024005074</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.7095669922860558</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3762018586691142</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.024380586562767</v>
+        <v>0.7204355686326651</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.04587818187954884</v>
+        <v>0.001936445864136438</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9132220137014836</v>
+        <v>1.004636791104984</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1972980545953467</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.03125611620768698</v>
+        <v>-0.04457655345150191</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.186809944462409</v>
+        <v>0.1019294515886751</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1310688615144554</v>
+        <v>-0.132954069635725</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1208335173134824</v>
+        <v>-0.1381821136848026</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1103506778152781</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.1208335173134826</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1280357344784944</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.003416596729815757</v>
-      </c>
+        <v>-0.03128360262353558</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3781,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06563715832679806</v>
+        <v>-0.1564204070376949</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01160242045765658</v>
+        <v>-0.07173108617818169</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.314556771252366</v>
+        <v>-0.546578367816291</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1226853743576179</v>
+        <v>0.3323157889297771</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1619647554362004</v>
+        <v>0.1725035540074816</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.96875</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3145567712523659</v>
+        <v>-0.4947041378614326</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3805760383096188</v>
+        <v>-0.04524548311185916</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6247288792953063</v>
+        <v>1.050866425988885</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.314556771252366</v>
+        <v>-0.5217129259898845</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5546687364230183</v>
+        <v>0.6694765506133715</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2672606271681597</v>
+        <v>-0.02774074654566472</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4944799882562489</v>
+        <v>0.9335751909150753</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.2466901429950641</v>
+        <v>-0.1232553819783047</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.02367058962467927</v>
+        <v>-0.2965522102697926</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4630706895890531</v>
+        <v>-0.1639199617993695</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3326847312828392</v>
+        <v>-0.15863582720605</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3887,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.08418383694879905</v>
+        <v>0.04338699625213849</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.02920866179305182</v>
+        <v>0.1481355426174482</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4784516009673341</v>
+        <v>-0.4525292958562871</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1864182836750916</v>
+        <v>0.2198882059250306</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2318852485805744</v>
+        <v>0.1822146302722975</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9825581395348837</v>
+        <v>0.992789794786467</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4784516009673341</v>
+        <v>-0.4465979192130792</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.05046952442555219</v>
+        <v>0.04565102522394171</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9502339793205756</v>
+        <v>0.9486776505374147</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4784516009673341</v>
+        <v>-0.4525292958562871</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.078778956966741</v>
+        <v>0.8854049026495785</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.02023939023278809</v>
+        <v>0.09801024904227296</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9617174557413284</v>
+        <v>1.23468409800299</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1972980545953466</v>
+        <v>-0.1235425903287488</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.006678250663948559</v>
+        <v>-0.1299359509522844</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1132390602515279</v>
+        <v>-0.08432174590467167</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1077192807880654</v>
+        <v>-0.04981466453266215</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1531733244392995</v>
+        <v>-0.2151786075399792</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.06199045142329562</v>
+        <v>-0.2607216941876583</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.0972088963852884</v>
+        <v>0.06160479252483286</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3995,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.004164963243092568</v>
+        <v>0.0652984675799877</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05466027935665152</v>
+        <v>0.1722467679949087</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2236726154223472</v>
+        <v>-0.3230679747701248</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1101179911983531</v>
+        <v>0.1977485909390823</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1289905573652467</v>
+        <v>0.1232138521937863</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9861918604651163</v>
+        <v>0.9794786466999446</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.07386684616010941</v>
+        <v>-0.2878756577967964</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.8653583358195547</v>
+        <v>0.3455561053418139</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1467040491131595</v>
+        <v>0.6115147226095258</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.110762561332304</v>
+        <v>-0.3230679747701248</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.07526118963350159</v>
+        <v>0.4959444642548201</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.4932128039473933</v>
+        <v>-0.1288012715775083</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.06709437493470524</v>
+        <v>0.6915872519743499</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.2236726154223472</v>
+        <v>-0.08899901788117059</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.08762281169460295</v>
+        <v>-0.1116643187270593</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.9768205669133476</v>
+        <v>0.1783056063688457</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.5384623149029638</v>
+        <v>-0.2460905927363767</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4101,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1023296153824207</v>
+        <v>0.1137003565875556</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.04643433118821649</v>
+        <v>0.2255078583660064</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4594211534155789</v>
+        <v>-0.440783672775422</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1930386481380992</v>
+        <v>0.1876000456361126</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2244579288858291</v>
+        <v>0.169841076621919</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9781976744186046</v>
+        <v>0.9822518025513034</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4594211534155789</v>
+        <v>-0.3927999588798716</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08879943824826841</v>
+        <v>0.1473020567802092</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9124383530361304</v>
+        <v>0.8343982945060628</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4594211534155789</v>
+        <v>-0.440783672775422</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.039165280601249</v>
+        <v>0.8341572482983763</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.03890992736753374</v>
+        <v>0.0681649624208589</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9264023767802955</v>
+        <v>1.163219998698781</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1972980545953468</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.009946786310846889</v>
+        <v>-0.07130274274158865</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1538593317123842</v>
+        <v>0.004694222957882577</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1247227815785514</v>
+        <v>-0.07564188582246567</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1390001476193516</v>
+        <v>-0.1622898619784522</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0277640180753207</v>
+        <v>-0.1888541202263548</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.1144126854097943</v>
+        <v>0.03274905157049623</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4407,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4437,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4449,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4495,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05165909023225956</v>
+        <v>0.09147296701545193</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.02760303608722836</v>
+        <v>0.0361281855360438</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04350725044042764</v>
+        <v>0.2171366704425773</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1729842864844607</v>
+        <v>0.2748323219326458</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.9811046511627907</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710507</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>-0.05638459704404664</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>1.055598642040589</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2411450120325238</v>
+        <v>1.329736496831094</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02426237512681706</v>
+        <v>0.09804077200338912</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8865399859777371</v>
+        <v>1.18544284932526</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02438206875344118</v>
+        <v>-0.197128506330739</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4589,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.02603552158627365</v>
+        <v>0.1729929842825908</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.01737883578080979</v>
+        <v>0.186809944462409</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.04267275457304354</v>
+        <v>-0.0116421001056547</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4691,67 +4692,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05784179673175083</v>
+        <v>-0.03081137871963469</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03364431698245673</v>
+        <v>-0.07995554818428363</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1513122874756199</v>
+        <v>-0.2466901429950641</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04250324024427887</v>
+        <v>0.0967716574308219</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1725355536639805</v>
+        <v>0.09708356730186078</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8206896551724138</v>
+        <v>0.3582848837209303</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1476887982658786</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.05934658112297364</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7556854484241026</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1513122874756199</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2411450120325238</v>
+        <v>-0.05186929266720175</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02426237512681706</v>
+        <v>-0.553131362600058</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.8865399859777371</v>
+        <v>-0.0462408020223753</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02438206875344118</v>
+        <v>-0.246690142995064</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.005879002574993963</v>
+        <v>-0.1120360736642554</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.005879002574994185</v>
+        <v>1.181895334740688</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5930309249039774</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1461547765376521</v>
+        <v>0.1280357344784944</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1193965406079239</v>
+        <v>-0.09250707423188109</v>
       </c>
     </row>
     <row r="6">
@@ -4801,73 +4802,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05166817489799835</v>
+        <v>0.1255881729100359</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.02761191294683218</v>
+        <v>0.06851352850921844</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04351329149989632</v>
+        <v>0.1718439122094128</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1729822371057482</v>
+        <v>0.2198628215274138</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.9752906976744186</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.152662932451571</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.05316417728627743</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7811368087626823</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1526629324515709</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2411450120325238</v>
+        <v>1.024380586562767</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02426237512681706</v>
+        <v>-0.04587818187954884</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8865399859777371</v>
+        <v>0.9132220137014836</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02438206875344118</v>
+        <v>-0.1972980545953467</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>8.638413173223114e-06</v>
+        <v>0.03125611620768698</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>8.638413173223114e-06</v>
+        <v>0.186809944462409</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1310688615144554</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.02674035919858642</v>
+        <v>-0.1208335173134824</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.01707348015973364</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.04457488782115671</v>
+        <v>-0.1208335173134826</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1461547765376521</v>
+        <v>0.1280357344784944</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.01697417431465009</v>
+        <v>-0.003416596729815757</v>
       </c>
     </row>
     <row r="7">
@@ -4913,58 +4914,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05876633863086822</v>
+        <v>0.06563715832679806</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.08029647908353266</v>
+        <v>0.01160242045765658</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07123814693034164</v>
+        <v>0.1226853743576179</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1469223854751648</v>
+        <v>0.1619647554362004</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.96875</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.3145567712523659</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>0.3805760383096188</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>0.6247288792953063</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.314556771252366</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1108233407723489</v>
+        <v>0.5546687364230183</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1267159617360623</v>
+        <v>-0.2672606271681597</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4074283857095624</v>
+        <v>0.4944799882562489</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.004653424491574576</v>
+        <v>-0.2466901429950641</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1050011642449078</v>
+        <v>-0.02367058962467927</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.4630706895890531</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1050011642449077</v>
+        <v>-0.3326847312828392</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5020,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02396438970952985</v>
+        <v>0.08418383694879905</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.0005418347863406225</v>
+        <v>0.02920866179305182</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04877515983624106</v>
+        <v>0.1864182836750916</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1663564626546698</v>
+        <v>0.2318852485805744</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9825581395348837</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>0.05046952442555219</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>0.9502339793205756</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4784516009673341</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2084603333825927</v>
+        <v>1.078778956966741</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.04995773739830589</v>
+        <v>-0.02023939023278809</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.766378783770956</v>
+        <v>0.9617174557413284</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1972980545953466</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.026334294810891</v>
+        <v>-0.006678250663948559</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.1132390602515279</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02633429481089078</v>
+        <v>-0.1077192807880654</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.0003067598780439607</v>
+        <v>-0.1531733244392995</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01708197101178344</v>
+        <v>-0.06199045142329562</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01706674477322134</v>
+        <v>-0.0972088963852884</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5128,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.05876633863086822</v>
+        <v>-0.004164963243092568</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.08029647908353266</v>
+        <v>-0.05466027935665152</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.2236726154223472</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07123814693034164</v>
+        <v>0.1101179911983531</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1469223854751648</v>
+        <v>0.1289905573652467</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9861918604651163</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.07386684616010941</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>0.8653583358195547</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>0.1467040491131595</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.110762561332304</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1108233407723489</v>
+        <v>0.07526118963350159</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1267159617360623</v>
+        <v>-0.4932128039473933</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4074283857095624</v>
+        <v>0.06709437493470524</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.004653424491574576</v>
+        <v>-0.2236726154223472</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1050011642449078</v>
+        <v>-0.08762281169460295</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.9768205669133476</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1050011642449077</v>
+        <v>-0.5384623149029638</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5234,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.02396438970952985</v>
+        <v>0.1023296153824207</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.0005418347863406225</v>
+        <v>0.04643433118821649</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.04877515983624106</v>
+        <v>0.1930386481380992</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1663564626546698</v>
+        <v>0.2244579288858291</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9781976744186046</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>0.08879943824826841</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>0.9124383530361304</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.4594211534155789</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2084603333825927</v>
+        <v>1.039165280601249</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04995773739830589</v>
+        <v>-0.03890992736753374</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.766378783770956</v>
+        <v>0.9264023767802955</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1972980545953468</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.026334294810891</v>
+        <v>0.009946786310846889</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.1538593317123842</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02633429481089078</v>
+        <v>-0.1247227815785514</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.0003067598780439607</v>
+        <v>-0.1390001476193516</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01708197101178344</v>
+        <v>-0.0277640180753207</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.01706674477322134</v>
+        <v>-0.1144126854097943</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5540,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5628,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.01467512388623127</v>
+        <v>0.04973873152688491</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.07574179554405092</v>
+        <v>0.03025445432880103</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1265862887534693</v>
+        <v>0.04449667859819988</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4823761383388722</v>
+        <v>0.1724104395842316</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9754098360655737</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4639662821985409</v>
+        <v>0.2411450120325238</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.05349836459816792</v>
+        <v>-0.02426237512681706</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8486470478528155</v>
+        <v>0.8865399859777371</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09627677960540704</v>
+        <v>-0.02438206875344118</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5722,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.02497427700722055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>0.005949654656603798</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.04263876767180749</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.1638459834801125</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.007527408169611949</v>
+        <v>-0.02359106487729901</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02402749571349339</v>
+        <v>0.01993225387337039</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03081450841426825</v>
+        <v>-0.04267275457304354</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,64 +5824,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2455390692211575</v>
+        <v>0.05793197056602595</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3127685021555703</v>
+        <v>0.03829561806025406</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1513122874756199</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2331756779481813</v>
+        <v>0.04235842469467958</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.409110167701781</v>
+        <v>0.1719400336247212</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.815068493150685</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1476161445200224</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.06411353994389812</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.7418909563662913</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1513122874756199</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.08853103608775714</v>
+        <v>0.2411450120325238</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2962294156833691</v>
+        <v>-0.02426237512681706</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1619333242562566</v>
+        <v>0.8865399859777371</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.05618776473478682</v>
+        <v>-0.02438206875344118</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2564507466298789</v>
+        <v>0.007805026901525958</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.007805026901525958</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2564507466298789</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1482515156944797</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1210794689914346</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5929,70 +5934,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.0211947856099941</v>
+        <v>0.05238245734370484</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1084153650093214</v>
+        <v>0.03284910975781519</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.152662932451571</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1384300825564587</v>
+        <v>0.04336503453908074</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4587075764668267</v>
+        <v>0.1723852648856539</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8698630136986302</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.1520874296386187</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05853160053355011</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.7643627937361653</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.152662932451571</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4122134237596116</v>
+        <v>0.2411450120325238</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08695826442291199</v>
+        <v>-0.02426237512681706</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7539851894004641</v>
+        <v>0.8865399859777371</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02438206875344118</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>0.002518460772590991</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.002518460772591213</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.02803474814585305</v>
+        <v>0.02674035919858619</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.0234637212516956</v>
+        <v>-0.01707348015973364</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.004680857223262946</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>0.04457488782115671</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1482515156944797</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.01442816182558482</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6037,19 +6046,19 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2455390692211575</v>
+        <v>-0.06048505743641064</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3127685021555703</v>
+        <v>-0.07792346284422524</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2331756779481813</v>
+        <v>0.07249837463053579</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.409110167701781</v>
+        <v>0.1464265982846205</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
@@ -6058,37 +6067,37 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08853103608775714</v>
+        <v>0.1108233407723489</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2962294156833691</v>
+        <v>-0.1267159617360623</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.1619333242562566</v>
+        <v>0.4074283857095624</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.05618776473478682</v>
+        <v>-0.004653424491574576</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2564507466298789</v>
+        <v>-0.1050011642449077</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2564507466298789</v>
+        <v>-0.1050011642449077</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6143,67 +6152,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0211947856099941</v>
+        <v>0.02209460229644522</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1084153650093214</v>
+        <v>0.003123429798272737</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1384300825564587</v>
+        <v>0.04993855307894733</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4587075764668267</v>
+        <v>0.165802462227193</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4122134237596116</v>
+        <v>0.2084603333825927</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08695826442291199</v>
+        <v>-0.04995773739830589</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7539851894004641</v>
+        <v>0.766378783770956</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>-0.02633429481089089</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>-0.02633429481089078</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.02803474814585305</v>
+        <v>-0.002809509248547726</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.0234637212516956</v>
+        <v>-0.0195427233501777</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.004680857223262946</v>
+        <v>0.01706674477322134</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6251,19 +6260,19 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2455390692211574</v>
+        <v>-0.06048505743641064</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.3127685021555702</v>
+        <v>-0.07792346284422524</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3068999359996033</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2331756779481812</v>
+        <v>0.07249837463053579</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4091101677017805</v>
+        <v>0.1464265982846205</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -6272,37 +6281,37 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3068999359996033</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02350067883024787</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3068999359996033</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08853103608775714</v>
+        <v>0.1108233407723489</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2962294156833691</v>
+        <v>-0.1267159617360623</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1619333242562566</v>
+        <v>0.4074283857095624</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.05618776473478648</v>
+        <v>-0.004653424491574576</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.2564507466298788</v>
+        <v>-0.1050011642449077</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2564507466298789</v>
+        <v>-0.1050011642449077</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6357,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.0211947856099941</v>
+        <v>0.02209460229644522</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.1084153650093214</v>
+        <v>0.003123429798272737</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1384300825564587</v>
+        <v>0.04993855307894733</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4587075764668267</v>
+        <v>0.165802462227193</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4122134237596116</v>
+        <v>0.2084603333825927</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.08695826442291199</v>
+        <v>-0.04995773739830589</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7539851894004641</v>
+        <v>0.766378783770956</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>-0.02633429481089089</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03535112732323886</v>
+        <v>-0.02633429481089078</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.02803474814585305</v>
+        <v>-0.002809509248547726</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0234637212516956</v>
+        <v>-0.0195427233501777</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.004680857223262946</v>
+        <v>0.01706674477322134</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6663,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6693,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6705,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6751,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1273573073874552</v>
+        <v>0.003147169989504262</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.06252517135729563</v>
+        <v>-0.09736796118354629</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1821400660530844</v>
+        <v>0.1245853659936119</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2502692357919135</v>
+        <v>0.4747180043938371</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3407563776045505</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04480797187624819</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.099812565704477</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3408596999336523</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7100769261764752</v>
+        <v>0.4473338296920579</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1123681313006502</v>
+        <v>-0.07564499099171129</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.32149125162987</v>
+        <v>0.7906539420355296</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1054534314823259</v>
+        <v>-0.09627677960540704</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6845,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.009125074064342265</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.09198904181424106</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1149439295311541</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.4227552867946717</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.4217964992394458</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.09195467631537591</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.7455172015271687</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.07820336667939509</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05860721376946743</v>
+        <v>0.005959149617997372</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1563845693517263</v>
+        <v>0.02402749571349339</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.18591720161202</v>
+        <v>-0.01764439545923246</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6947,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.1752251904394864</v>
+        <v>-0.2455266269195334</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2226563928606533</v>
+        <v>-0.3211246970038566</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.312323466053521</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2279280762871689</v>
+        <v>0.2335747961321316</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2065218374947578</v>
+        <v>0.4025630958014377</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2861173531946565</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03435966625902531</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9234616899078895</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2977686466384254</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1553366834891103</v>
+        <v>0.08854898775486908</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2484784234184519</v>
+        <v>-0.3047867128233982</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.28908990099622</v>
+        <v>0.1565086331159856</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1192418798084101</v>
+        <v>-0.05618776473478682</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2683998195107709</v>
+        <v>-0.2478936335050813</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.08288138489888741</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3243949053962718</v>
+        <v>-0.2478936335050813</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.8786786156143458</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4669938870301228</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7057,19 +7062,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.09567692788478765</v>
+        <v>-0.01916549323471695</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1476827968691763</v>
+        <v>-0.1174449003406536</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3207476547189958</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2093242434085273</v>
+        <v>0.1362899943774674</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2257235656319314</v>
+        <v>0.4513537297044311</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -7078,53 +7083,49 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3155344176362946</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.008263340609595105</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.018407109114682</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3156416929678373</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3212104383572656</v>
+        <v>0.4151412728259709</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1405811259868913</v>
+        <v>-0.09620510682779526</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5977898570891276</v>
+        <v>0.7337542168171252</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1054534314823259</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1978381067038132</v>
+        <v>-0.02224266178655987</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03825893662286561</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.227397073118031</v>
+        <v>-0.02224266178655998</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1478988313601229</v>
+        <v>-0.02803474814585316</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1021508206349402</v>
+        <v>-0.0234637212516956</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.05095289028112149</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.8786786156143458</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.1063115227943896</v>
-      </c>
+        <v>-0.004680857223262946</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7169,58 +7170,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2574679878740029</v>
+        <v>-0.2455266269195334</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1851534385211067</v>
+        <v>-0.3211246970038566</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1789082384476008</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06132010632651158</v>
+        <v>0.2335747961321316</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1317362929031493</v>
+        <v>0.4025630958014377</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9200779727095516</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.06771588773477133</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3508061689643462</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.218557271773101</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1789082384476008</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.348803408028326</v>
+        <v>0.08854898775486908</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1226324947644001</v>
+        <v>-0.3047867128233982</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6491418538694487</v>
+        <v>0.1565086331159856</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.104492178039316</v>
+        <v>-0.05618776473478682</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1154121054912636</v>
+        <v>-0.2478936335050813</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.414172364501078</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2112615594176298</v>
+        <v>-0.2478936335050813</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7275,67 +7276,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1337001688040274</v>
+        <v>-0.01916549323471695</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.06850326709444654</v>
+        <v>-0.1174449003406536</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2667855627451129</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1398699131552316</v>
+        <v>0.1362899943774674</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1988129630048607</v>
+        <v>0.4513537297044311</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.266785562745113</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06236990632728068</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8610671246074929</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2667855627451129</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.546205463504696</v>
+        <v>0.4151412728259709</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.005773281726672463</v>
+        <v>-0.09620510682779526</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.01651766872721</v>
+        <v>0.7337542168171252</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.104492178039316</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.005626309755574432</v>
+        <v>-0.02224266178655987</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1122055828020825</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.09582695384246598</v>
+        <v>-0.02224266178655998</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.06823243651806776</v>
+        <v>-0.02803474814585316</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.03820440683881721</v>
+        <v>-0.0234637212516956</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1106647234752383</v>
+        <v>-0.004680857223262946</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7383,68 +7384,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1601660237560227</v>
+        <v>-0.2455266269195333</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.09344712196966198</v>
+        <v>-0.3211246970038565</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.104492178039316</v>
+        <v>-0.3068999359996033</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.01718187800819657</v>
+        <v>0.2335747961321315</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.07065396255489076</v>
+        <v>0.4025630958014372</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.2261208576998051</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3068999359996033</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>-0.02350067883024787</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.3068999359996033</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1471983485748272</v>
+        <v>0.08854898775486886</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2537722346277178</v>
+        <v>-0.3047867128233983</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2739440231404645</v>
+        <v>0.1565086331159852</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1044921780393159</v>
+        <v>-0.05618776473478648</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.02910232288696357</v>
+        <v>-0.2478936335050812</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.534036497899318</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3291539514892914</v>
+        <v>-0.2478936335050815</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.1128423029659751</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.1012753618169033</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7493,74 +7490,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.08759852036635896</v>
+        <v>-0.01916549323471695</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02505283519934176</v>
+        <v>-0.1174449003406536</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1150830920148228</v>
+        <v>0.1362899943774674</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1805580562386028</v>
+        <v>0.4513537297044311</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4266596658043573</v>
+        <v>0.4151412728259709</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.07198867947942134</v>
+        <v>-0.09620510682779526</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.794036526182875</v>
+        <v>0.7337542168171252</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1044921780393161</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03526724558448424</v>
+        <v>-0.02224266178655987</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1563845693517263</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1657336322324426</v>
+        <v>-0.02224266178655998</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.02479301788410715</v>
+        <v>-0.02803474814585316</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>-0.0234637212516956</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02479301788410737</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.1128423029659751</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>-0.01183659930796777</v>
-      </c>
+        <v>-0.004680857223262946</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7803,28 +7796,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.179974191375289</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450096</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7833,10 +7826,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.5373300241683001</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7845,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7891,49 +7884,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.04333413134981978</v>
+        <v>0.1273573073874552</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.04103642873724656</v>
+        <v>0.06252517135729563</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09995226162961648</v>
+        <v>0.1821400660530844</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2763396704990286</v>
+        <v>0.2502692357919135</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.3407563776045505</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04972520692256377</v>
+        <v>-0.04480797187624819</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.827936916176494</v>
+        <v>1.099812565704477</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.3408596999336523</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1747232527765494</v>
+        <v>0.7100769261764752</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.08646228085337915</v>
+        <v>0.1123681313006502</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.61112221494444</v>
+        <v>1.32149125162987</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07027295871809192</v>
+        <v>-0.1054534314823259</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7985,58 +7978,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.002647486103235841</v>
+        <v>-0.05860721376946743</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03868014017475119</v>
+        <v>0.1563845693517263</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03978859774004517</v>
+        <v>-0.18591720161202</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8087,67 +8080,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.1752251904394864</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.2226563928606533</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.312323466053521</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.2279280762871689</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2065218374947578</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2861173531946565</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.03435966625902531</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.9234616899078895</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2977686466384254</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1553366834891103</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2484784234184519</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.28908990099622</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1192418798084101</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06086847685246877</v>
+        <v>-0.2683998195107709</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.234934132106791</v>
+        <v>0.08288138489888741</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1409513679546353</v>
+        <v>-0.3243949053962718</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.8786786156143458</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1282572424698077</v>
+        <v>-0.4669938870301228</v>
       </c>
     </row>
     <row r="6">
@@ -8197,19 +8190,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.09567692788478765</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.1476827968691763</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3207476547189958</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.2093242434085273</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2257235656319314</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -8218,52 +8211,52 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3155344176362946</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>-0.008263340609595105</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>1.018407109114682</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3156416929678373</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3212104383572656</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.1405811259868913</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.5977898570891276</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1054534314823259</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.002647486103235841</v>
+        <v>-0.1978381067038132</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03868014017475119</v>
+        <v>0.03825893662286561</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03978859774004517</v>
+        <v>-0.227397073118031</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1478988313601229</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1021508206349402</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>-0.05095289028112149</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.8786786156143458</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.04877167935164584</v>
+        <v>-0.1063115227943896</v>
       </c>
     </row>
     <row r="7">
@@ -8309,68 +8302,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.2574679878740029</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1851534385211067</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1789082384476008</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.06132010632651158</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1317362929031493</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>0.9200779727095516</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.06771588773477133</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.3508061689643462</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.218557271773101</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1789082384476008</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.348803408028326</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1226324947644001</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.6491418538694487</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.104492178039316</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06086847685246877</v>
+        <v>0.1154121054912636</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.234934132106791</v>
+        <v>0.414172364501078</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1409513679546353</v>
+        <v>-0.2112615594176298</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.03966424779839195</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.03329611901649576</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8419,74 +8408,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.1337001688040274</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.06850326709444654</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2667855627451129</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1398699131552316</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1988129630048607</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.266785562745113</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.06236990632728068</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.8610671246074929</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2667855627451129</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.546205463504696</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>0.005773281726672463</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>1.01651766872721</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.104492178039316</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.002647486103235841</v>
+        <v>0.005626309755574432</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03868014017475119</v>
+        <v>0.1122055828020825</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03978859774004517</v>
+        <v>-0.09582695384246598</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0</v>
+        <v>0.06823243651806776</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.03820440683881721</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.03966424779839195</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.02521277934010779</v>
-      </c>
+        <v>0.1106647234752383</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8531,67 +8516,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1601660237560227</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.09344712196966198</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.104492178039316</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.01718187800819657</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.07065396255489076</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.2261208576998051</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1471983485748272</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2537722346277178</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2739440231404645</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1044921780393159</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.06086847685246877</v>
+        <v>0.02910232288696357</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.234934132106791</v>
+        <v>0.534036497899318</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1409513679546353</v>
+        <v>-0.3291539514892914</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.1128423029659751</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.1282572424698077</v>
+        <v>-0.1012753618169033</v>
       </c>
     </row>
     <row r="10">
@@ -8641,73 +8626,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.08759852036635896</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.02505283519934176</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1150830920148228</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1805580562386028</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.4266596658043573</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.07198867947942134</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.794036526182875</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1044921780393161</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.002647486103235841</v>
+        <v>-0.03526724558448424</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.03868014017475119</v>
+        <v>0.1563845693517263</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03978859774004517</v>
+        <v>-0.1657336322324426</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0</v>
+        <v>0.02479301788410715</v>
       </c>
       <c r="AC10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
+        <v>0.02479301788410737</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.1659072706450004</v>
+        <v>0.1128423029659751</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>-0.04877167935164584</v>
+        <v>-0.01183659930796777</v>
       </c>
     </row>
   </sheetData>
@@ -8721,7 +8706,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947872</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.03851870301874494</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.04323081008140095</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.09947831423738925</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2749222742536829</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.04972520692256377</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.827936916176494</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1806362845026359</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.08855271493049111</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.6116165647247094</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.07027295871809192</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.004135839319184487</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.03868014017475119</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.04122152512392507</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.05573222561184799</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.234934132106791</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1451104976661594</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1282572424698077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.004135839319184487</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.03868014017475119</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.04122152512392507</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.04877167935164584</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.05573222561184799</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.234934132106791</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1451104976661594</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.03966424779839195</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.03329611901649576</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.004135839319184487</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.03868014017475119</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.04122152512392507</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.03966424779839195</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.02521277934010779</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.05573222561184799</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.234934132106791</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1451104976661594</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.1282572424698077</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.004135839319184487</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.03868014017475119</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.04122152512392507</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.1659072706450004</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.04877167935164584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8922,23 +10053,23 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8968,19 +10099,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -9013,24 +10146,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9061,21 +10192,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9092,37 +10225,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9149,27 +10280,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9196,25 +10325,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9241,25 +10372,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,24 +10419,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -9333,27 +10464,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,24 +10499,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9397,10 +10526,10 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,37 +10546,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,25 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9519,25 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9564,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9611,32 +10744,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
